--- a/public/samples/commissions_template.xlsx
+++ b/public/samples/commissions_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NextSAAS\agencies\public\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B833675A-5427-4902-A152-39CB1F4E56E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840EBEE6-B3AD-4008-8F62-D47454343CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>University Name*</t>
   </si>
@@ -135,6 +135,51 @@
   </si>
   <si>
     <t>remark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aberystwyth University </t>
+  </si>
+  <si>
+    <t>Masters</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Catholic University Of America</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>Standard commission</t>
+  </si>
+  <si>
+    <t>Karlshochschule International University</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>percentage</t>
+  </si>
+  <si>
+    <t>University of Cambridge</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -552,10 +597,98 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="6" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
